--- a/Befehle.xlsx
+++ b/Befehle.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ifmworld-my.sharepoint.com/personal/nathalie_nuber_ifm_com/Documents/Documents/DHBW/Bachelorarbeit/Bachelorarbeit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="8_{4E832951-3784-4F6E-A2CB-CDD290849CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18ED7E85-F3D1-4205-AC98-8CA9F70BEC1E}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="8_{4E832951-3784-4F6E-A2CB-CDD290849CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{152A245A-99EE-4111-9CDE-D6BD1E964D15}"/>
   <bookViews>
-    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{0D17E905-4E7E-44FA-82A1-96251D2E0DB1}"/>
+    <workbookView xWindow="0" yWindow="9840" windowWidth="16200" windowHeight="12255" xr2:uid="{0D17E905-4E7E-44FA-82A1-96251D2E0DB1}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="77">
   <si>
     <t>Option</t>
   </si>
@@ -230,13 +230,438 @@
       </rPr>
       <t xml:space="preserve">) </t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> --max-parallelism 2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -e</t>
+  </si>
+  <si>
+    <t>eth1: verwendet ausdrücklich das USB-ethernet-interface</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -sS </t>
+  </si>
+  <si>
+    <t>TCP-SYN-Scan</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -sV</t>
+  </si>
+  <si>
+    <t>Service-und Versionserkennung</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -p</t>
+  </si>
+  <si>
+    <t>alle TCP-Ports von 1 bis 65535</t>
+  </si>
+  <si>
+    <t>normales, eher kontrolliertes Timing</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> --max-parallelism 2</t>
+  </si>
+  <si>
+    <t>maximal zwei parallele Probes</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -oA cm001_srio</t>
+  </si>
+  <si>
+    <t>Ausgabe als .nmap, .gnmap, .xml</t>
+  </si>
+  <si>
+    <t>Teil</t>
+  </si>
+  <si>
+    <t>Erklärung</t>
+  </si>
+  <si>
+    <t>for p in ... ; do ... ; done</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Iteriert über die Liste der Pfade, jeder wird nacheinander in </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>$p</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> gespeichert</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>\</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> am Zeilenende</t>
+    </r>
+  </si>
+  <si>
+    <t>Zeilenumbruch-Escape, damit die lange Liste über mehrere Zeilen lesbar bleibt – funktioniert korrekt in Bash</t>
+  </si>
+  <si>
+    <t>echo "== $p =="</t>
+  </si>
+  <si>
+    <t>Gibt eine Überschrift pro Pfad aus, damit du in der Ausgabedatei später erkennst, welcher Wert zu welchem Endpunkt gehört</t>
+  </si>
+  <si>
+    <t>echo; done</t>
+  </si>
+  <si>
+    <t>Leerzeile nach jeder Ausgabe für bessere Lesbarkeit</t>
+  </si>
+  <si>
+    <t>| tee cm_rq004-01_inventory.txt</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Die </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>gesamte</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Schleifenausgabe wird gesammelt in die Datei geschrieben (und gleichzeitig am Bildschirm angezeigt)</t>
+    </r>
+  </si>
+  <si>
+    <t>Befehl</t>
+  </si>
+  <si>
+    <r>
+      <t>binwalk</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (ohne Flag)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Scannt die Datei nach bekannten </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Datei-Signaturen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> innerhalb des Binärblobs (z. B. eingebettete ZIP-Archive, Dateisysteme, Header-Magic-Bytes bekannter Formate wie ELF, JFFS2, LZMA-komprimierte Bereiche etc.) – zeigt dir eine Liste "Was für Strukturen stecken an welchem Offset in dieser Datei?"</t>
+    </r>
+  </si>
+  <si>
+    <t>binwalk -E</t>
+  </si>
+  <si>
+    <r>
+      <t>Entropie-Analyse</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> – zeichnet grafisch/tabellarisch den "Zufälligkeitsgrad" jedes Datenabschnitts. Wichtig: Verschlüsselte </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>und</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> komprimierte Daten sehen entropisch ähnlich aus (beide nahe am Maximalwert 8.0) – hohe Entropie allein beweist also </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>nicht</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Verschlüsselung, sondern kann auch einfach Kompression sein. Das ist wichtig für die Interpretation später.</t>
+    </r>
+  </si>
+  <si>
+    <t>strings -n 8</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Extrahiert alle </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>lesbaren Zeichenketten</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> mit mindestens 8 aufeinanderfolgenden druckbaren Zeichen – nützlich, um z. B. Versionsstrings, Debug-Pfade, oder Klartext-Hinweise auf Zertifikatsnamen/Signaturbibliotheken zu finden</t>
+    </r>
+  </si>
+  <si>
+    <t>Korrigiert</t>
+  </si>
+  <si>
+    <t>Grund</t>
+  </si>
+  <si>
+    <r>
+      <t>-i eth1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> fest verdrahtet</t>
+    </r>
+  </si>
+  <si>
+    <t>-i "$IFACE"</t>
+  </si>
+  <si>
+    <t>Konsistenz mit den anderen Tests, falls sich das Interface mal ändert</t>
+  </si>
+  <si>
+    <r>
+      <t>ip.addr==192.168.0.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> fest verdrahtet</t>
+    </r>
+  </si>
+  <si>
+    <t>ip.addr==$SRIO</t>
+  </si>
+  <si>
+    <t>dito</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Kein </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>&amp;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, blockiert das Terminal</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>&amp;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>TSHARK_PID=$!</t>
+    </r>
+  </si>
+  <si>
+    <t>Ermöglicht Ablauf im Hintergrund</t>
+  </si>
+  <si>
+    <r>
+      <t>Kein curl-Trigger</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> – Kernfehler!</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>curl -s http://$SRIO/deviceinfo/swinfo/scpuversion/getdata</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ergänzt</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ohne diesen Schritt zeichnet tshark </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>keinen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> relevanten Traffic auf</t>
+    </r>
+  </si>
+  <si>
+    <t>tshark läuft unbegrenzt weiter</t>
+  </si>
+  <si>
+    <r>
+      <t>sleep 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>sudo kill $TSHARK_PID</t>
+    </r>
+  </si>
+  <si>
+    <t>Kontrollierter, definierter Abschluss der Aufzeichnung</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -269,6 +694,13 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -349,7 +781,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -369,6 +801,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -378,8 +813,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -396,6 +831,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -715,16 +1154,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F445D489-FD34-471C-A2D7-3CFE1A8CB8C6}">
-  <dimension ref="A1:D18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <dimension ref="A1:L46"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="14.7109375" customWidth="1"/>
-    <col min="3" max="3" width="48.7109375" customWidth="1"/>
-    <col min="4" max="4" width="25.5703125" customWidth="1"/>
+    <col min="2" max="2" width="14.7265625" customWidth="1"/>
+    <col min="3" max="3" width="48.7265625" customWidth="1"/>
+    <col min="4" max="4" width="25.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" thickBot="1"/>
-    <row r="2" spans="1:4" ht="17.25" thickBot="1">
+    <row r="1" spans="1:4" ht="15" thickBot="1"/>
+    <row r="2" spans="1:4" ht="17" thickBot="1">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -735,127 +1174,127 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="33.75" thickBot="1">
-      <c r="A3" s="10"/>
+    <row r="3" spans="1:4" ht="33.5" thickBot="1">
+      <c r="A3" s="7"/>
       <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="10"/>
-    </row>
-    <row r="4" spans="1:4" ht="17.25" thickBot="1">
-      <c r="A4" s="10"/>
+      <c r="D3" s="7"/>
+    </row>
+    <row r="4" spans="1:4" ht="17" thickBot="1">
+      <c r="A4" s="7"/>
       <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="10"/>
-    </row>
-    <row r="5" spans="1:4" ht="60.75" thickBot="1">
-      <c r="A5" s="10"/>
+      <c r="D4" s="7"/>
+    </row>
+    <row r="5" spans="1:4" ht="58.5" thickBot="1">
+      <c r="A5" s="7"/>
       <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="7" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="33.75" thickBot="1">
-      <c r="A6" s="10"/>
+    <row r="6" spans="1:4" ht="33.5" thickBot="1">
+      <c r="A6" s="7"/>
       <c r="B6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="10"/>
-    </row>
-    <row r="7" spans="1:4" ht="17.25" thickBot="1">
-      <c r="A7" s="10"/>
+      <c r="D6" s="7"/>
+    </row>
+    <row r="7" spans="1:4" ht="17" thickBot="1">
+      <c r="A7" s="7"/>
       <c r="B7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="10"/>
-    </row>
-    <row r="8" spans="1:4" ht="33.75" thickBot="1">
-      <c r="A8" s="10"/>
+      <c r="D7" s="7"/>
+    </row>
+    <row r="8" spans="1:4" ht="33.5" thickBot="1">
+      <c r="A8" s="7"/>
       <c r="B8" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="30">
-      <c r="A9" s="10"/>
-      <c r="B9" s="7" t="s">
+    <row r="9" spans="1:4" ht="29">
+      <c r="A9" s="7"/>
+      <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="16.5">
-      <c r="A10" s="10"/>
-      <c r="B10" s="8"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="9"/>
       <c r="C10" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="10"/>
+      <c r="D10" s="7"/>
     </row>
     <row r="11" spans="1:4" ht="16.5">
-      <c r="A11" s="10"/>
-      <c r="B11" s="8"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="9"/>
       <c r="C11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="10"/>
-    </row>
-    <row r="12" spans="1:4" ht="17.25" thickBot="1">
-      <c r="A12" s="10"/>
-      <c r="B12" s="9"/>
+      <c r="D11" s="7"/>
+    </row>
+    <row r="12" spans="1:4" ht="17" thickBot="1">
+      <c r="A12" s="7"/>
+      <c r="B12" s="10"/>
       <c r="C12" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="10"/>
-    </row>
-    <row r="13" spans="1:4" ht="17.25" thickBot="1">
-      <c r="A13" s="10"/>
+      <c r="D12" s="7"/>
+    </row>
+    <row r="13" spans="1:4" ht="17" thickBot="1">
+      <c r="A13" s="7"/>
       <c r="B13" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="10"/>
+      <c r="D13" s="7"/>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
     </row>
     <row r="18" spans="2:3">
       <c r="B18" t="s">
@@ -863,6 +1302,212 @@
       </c>
       <c r="C18" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3">
+      <c r="B21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3">
+      <c r="B23" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3">
+      <c r="B24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3">
+      <c r="B25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3">
+      <c r="B26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3">
+      <c r="B27" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3">
+      <c r="B28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3">
+      <c r="B29" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="15" thickBot="1"/>
+    <row r="38" spans="1:12" ht="17" thickBot="1">
+      <c r="A38" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="83" thickBot="1">
+      <c r="A39" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="132.5" thickBot="1">
+      <c r="A40" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="182" thickBot="1">
+      <c r="A41" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="409.6" thickBot="1">
+      <c r="A42" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I42" s="3">
+        <v>1</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="409.6" thickBot="1">
+      <c r="A43" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="I43" s="3">
+        <v>2</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="409.6" thickBot="1">
+      <c r="D44" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="I44" s="3">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="132.5" thickBot="1">
+      <c r="I45" s="3">
+        <v>4</v>
+      </c>
+      <c r="J45" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="116" thickBot="1">
+      <c r="I46" s="3">
+        <v>5</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/Befehle.xlsx
+++ b/Befehle.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ifmworld-my.sharepoint.com/personal/nathalie_nuber_ifm_com/Documents/Documents/DHBW/Bachelorarbeit/Bachelorarbeit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="55" documentId="8_{4E832951-3784-4F6E-A2CB-CDD290849CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{152A245A-99EE-4111-9CDE-D6BD1E964D15}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="8_{4E832951-3784-4F6E-A2CB-CDD290849CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB3ED896-4ED1-41DE-9F97-852CEC47B8D9}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="9840" windowWidth="16200" windowHeight="12255" xr2:uid="{0D17E905-4E7E-44FA-82A1-96251D2E0DB1}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{0D17E905-4E7E-44FA-82A1-96251D2E0DB1}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="74">
   <si>
     <t>Option</t>
   </si>
@@ -361,9 +361,6 @@
     </r>
   </si>
   <si>
-    <t>Befehl</t>
-  </si>
-  <si>
     <r>
       <t>binwalk</t>
     </r>
@@ -482,12 +479,6 @@
       </rPr>
       <t xml:space="preserve"> mit mindestens 8 aufeinanderfolgenden druckbaren Zeichen – nützlich, um z. B. Versionsstrings, Debug-Pfade, oder Klartext-Hinweise auf Zertifikatsnamen/Signaturbibliotheken zu finden</t>
     </r>
-  </si>
-  <si>
-    <t>Korrigiert</t>
-  </si>
-  <si>
-    <t>Grund</t>
   </si>
   <si>
     <r>
@@ -661,7 +652,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -804,6 +795,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -811,9 +805,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1154,16 +1145,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F445D489-FD34-471C-A2D7-3CFE1A8CB8C6}">
-  <dimension ref="A1:L46"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <dimension ref="A1:J62"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="14.7265625" customWidth="1"/>
     <col min="3" max="3" width="48.7265625" customWidth="1"/>
     <col min="4" max="4" width="25.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" thickBot="1"/>
-    <row r="2" spans="1:4" ht="17" thickBot="1">
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1174,7 +1165,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="33.5" thickBot="1">
+    <row r="3" spans="1:4" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="7"/>
       <c r="B3" s="2" t="s">
         <v>2</v>
@@ -1184,7 +1175,7 @@
       </c>
       <c r="D3" s="7"/>
     </row>
-    <row r="4" spans="1:4" ht="17" thickBot="1">
+    <row r="4" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="7"/>
       <c r="B4" s="2" t="s">
         <v>4</v>
@@ -1194,7 +1185,7 @@
       </c>
       <c r="D4" s="7"/>
     </row>
-    <row r="5" spans="1:4" ht="58.5" thickBot="1">
+    <row r="5" spans="1:4" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="7"/>
       <c r="B5" s="2" t="s">
         <v>6</v>
@@ -1206,7 +1197,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="33.5" thickBot="1">
+    <row r="6" spans="1:4" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="7"/>
       <c r="B6" s="2" t="s">
         <v>8</v>
@@ -1216,7 +1207,7 @@
       </c>
       <c r="D6" s="7"/>
     </row>
-    <row r="7" spans="1:4" ht="17" thickBot="1">
+    <row r="7" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="7"/>
       <c r="B7" s="2" t="s">
         <v>10</v>
@@ -1226,7 +1217,7 @@
       </c>
       <c r="D7" s="7"/>
     </row>
-    <row r="8" spans="1:4" ht="33.5" thickBot="1">
+    <row r="8" spans="1:4" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="7"/>
       <c r="B8" s="2" t="s">
         <v>24</v>
@@ -1238,9 +1229,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="29">
+    <row r="9" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="7"/>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="9" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="4" t="s">
@@ -1250,31 +1241,31 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="16.5">
+    <row r="10" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A10" s="7"/>
-      <c r="B10" s="9"/>
+      <c r="B10" s="10"/>
       <c r="C10" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D10" s="7"/>
     </row>
-    <row r="11" spans="1:4" ht="16.5">
+    <row r="11" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A11" s="7"/>
-      <c r="B11" s="9"/>
+      <c r="B11" s="10"/>
       <c r="C11" s="5" t="s">
         <v>16</v>
       </c>
       <c r="D11" s="7"/>
     </row>
-    <row r="12" spans="1:4" ht="17" thickBot="1">
+    <row r="12" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="7"/>
-      <c r="B12" s="10"/>
+      <c r="B12" s="11"/>
       <c r="C12" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D12" s="7"/>
     </row>
-    <row r="13" spans="1:4" ht="17" thickBot="1">
+    <row r="13" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="7"/>
       <c r="B13" s="2" t="s">
         <v>18</v>
@@ -1284,19 +1275,19 @@
       </c>
       <c r="D13" s="7"/>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
     </row>
-    <row r="18" spans="2:3">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>23</v>
       </c>
@@ -1304,12 +1295,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="2:3">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="2:3">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>28</v>
       </c>
@@ -1317,7 +1308,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="2:3">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>30</v>
       </c>
@@ -1325,7 +1316,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="2:3">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>32</v>
       </c>
@@ -1333,7 +1324,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="2:3">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>34</v>
       </c>
@@ -1341,7 +1332,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:3">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>24</v>
       </c>
@@ -1349,7 +1340,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="2:3">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>37</v>
       </c>
@@ -1357,7 +1348,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="2:3">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>39</v>
       </c>
@@ -1365,8 +1356,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="15" thickBot="1"/>
-    <row r="38" spans="1:12" ht="17" thickBot="1">
+    <row r="37" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="38" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="1" t="s">
         <v>41</v>
       </c>
@@ -1374,7 +1365,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="83" thickBot="1">
+    <row r="39" spans="1:10" ht="83" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="2" t="s">
         <v>43</v>
       </c>
@@ -1382,7 +1373,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="132.5" thickBot="1">
+    <row r="40" spans="1:10" ht="132.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="2" t="s">
         <v>45</v>
       </c>
@@ -1390,124 +1381,119 @@
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="182" thickBot="1">
+    <row r="41" spans="1:10" ht="198.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="409.6" thickBot="1">
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+    </row>
+    <row r="42" spans="1:10" ht="66.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="2" t="s">
         <v>49</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="I42" s="3">
-        <v>1</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="409.6" thickBot="1">
+    </row>
+    <row r="43" spans="1:10" ht="165.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="2" t="s">
         <v>51</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D43" s="2" t="s">
+    </row>
+    <row r="44" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+    </row>
+    <row r="45" spans="1:10" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B46" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="E43" s="11" t="s">
+    </row>
+    <row r="47" spans="1:10" ht="314" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="I43" s="3">
-        <v>2</v>
-      </c>
-      <c r="J43" s="2" t="s">
+      <c r="B47" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="58" spans="1:4" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A58" s="3"/>
+      <c r="B58" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="46" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A59" s="3"/>
+      <c r="B59" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A60" s="3"/>
+      <c r="B60" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="K43" s="2" t="s">
+      <c r="C60" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="L43" s="3" t="s">
+      <c r="D60" s="3" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="409.6" thickBot="1">
-      <c r="D44" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="I44" s="3">
-        <v>3</v>
-      </c>
-      <c r="J44" s="3" t="s">
+    <row r="61" spans="1:4" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A61" s="3"/>
+      <c r="B61" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K44" s="2" t="s">
+      <c r="C61" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="L44" s="3" t="s">
+      <c r="D61" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="132.5" thickBot="1">
-      <c r="I45" s="3">
-        <v>4</v>
-      </c>
-      <c r="J45" s="11" t="s">
+    <row r="62" spans="1:4" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A62" s="3"/>
+      <c r="B62" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="K45" s="2" t="s">
+      <c r="C62" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="L45" s="3" t="s">
+      <c r="D62" s="3" t="s">
         <v>73</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" ht="116" thickBot="1">
-      <c r="I46" s="3">
-        <v>5</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="K46" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>76</v>
       </c>
     </row>
   </sheetData>
